--- a/MedTech_Deals.xlsx
+++ b/MedTech_Deals.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://beacononehcp-my.sharepoint.com/personal/hannah_peric_beacononehcp_com/Documents/Documents/medtech-dashboard/medtech-dashboard/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="301" documentId="13_ncr:1_{A8E36CAE-087B-4CF0-B739-AC648A6297F4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E0016D1E-8B5A-48A1-9F12-3943AD40A33B}"/>
+  <xr:revisionPtr revIDLastSave="525" documentId="13_ncr:1_{A8E36CAE-087B-4CF0-B739-AC648A6297F4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D3383211-A482-4276-8627-9F550AB762A8}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="YTD M&amp;A Activity" sheetId="1" r:id="rId1"/>
@@ -19,14 +19,14 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'YTD Investment Activity'!$A$1:$I$181</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'YTD M&amp;A Activity'!$A$1:$I$105</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'YTD M&amp;A Activity'!$A$1:$I$111</definedName>
   </definedNames>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2224" uniqueCount="910">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2454" uniqueCount="1003">
   <si>
     <t>Company</t>
   </si>
@@ -2756,6 +2756,286 @@
   </si>
   <si>
     <t>Scalewolf</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Laborie </t>
+  </si>
+  <si>
+    <t>Organon</t>
+  </si>
+  <si>
+    <t>Laborie Medical Technologies has struck a deal to buy a post-childbirth medical device from Organon for $440 million upfront, the companies said Friday. The acquisition covers the Jada system, a treatment for abnormal postpartum uterine bleeding or hemorrhage, and around 100 employees who will transfer to Laborie as part of the deal.</t>
+  </si>
+  <si>
+    <t>November</t>
+  </si>
+  <si>
+    <t>Synchron</t>
+  </si>
+  <si>
+    <t>Synchron, a New York, NY-based manufacturer of non-surgical brain-computer interface technology, said it has raised a $200 million series D round. The funds are expected to accelerate commercialization of the company’s first-generation Stentrode BCI platform, while advancing development of a frontier next-generation interface.</t>
+  </si>
+  <si>
+    <t>Double Point Ventures, ARCH Ventures, Khosla Ventures, Bezos Expeditions, NTI, METIS, Australian National Reconstruction Fund (NRF), T.Rx Capital, Qatar Investment Authority (QIA), K5 Global,Protocol Labs, IQT</t>
+  </si>
+  <si>
+    <t>Qiagen</t>
+  </si>
+  <si>
+    <t>Parse Biosciences</t>
+  </si>
+  <si>
+    <t>Parse’s Evercode enables researchers to profile gene expression in individual cells at scale. Qiagen has identified Parse’s technology as complementary to its sample technology and bioinformatic businesses.</t>
+  </si>
+  <si>
+    <t>AtaCor Medical</t>
+  </si>
+  <si>
+    <t>Privately-held medical device company focused on transforming cardiac rhythm management systems, announced today that it has entered into a financing of up to $75 million. The proceeds will fund the company's U.S. FDA Pivotal Study evaluating AtaCor's parasternal extravascular implantable cardioverter-defibrillator (EV-ICD) system for the treatment of life-threatening ventricular tachyarrhythmias.</t>
+  </si>
+  <si>
+    <t>Arboretum Ventures, Broadview Ventures, Longview Ventures, Hatteras Venture Partners, Catalyst Health Ventures, and BayMed Venture Partners.</t>
+  </si>
+  <si>
+    <t>Cornerstone Robotics</t>
+  </si>
+  <si>
+    <t>Cornerstone develops an autonomous endoscopic robotic surgery platform. It equipped its laparoscopic surgical robot with AI-powered embodied intelligence.</t>
+  </si>
+  <si>
+    <t>Hong Kong Investment Corporation</t>
+  </si>
+  <si>
+    <t>Precision Neuroscience</t>
+  </si>
+  <si>
+    <t>SCI Ventures</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Precision develops an ultra-thin cortical electrode array enabling BCI technology that aims to address paralysis. </t>
+  </si>
+  <si>
+    <t>Clarity</t>
+  </si>
+  <si>
+    <t>Series B funding to commercialize a platform that predicts a woman’s five-year risk of breast cancer. The Clairity Breast platform uses artificial intelligence to analyze 2D mammogram images.</t>
+  </si>
+  <si>
+    <t>ACE Global Equity, Santé Ventures, Breast Cancer Research Foundation</t>
+  </si>
+  <si>
+    <t>Sovato</t>
+  </si>
+  <si>
+    <t>Beringea</t>
+  </si>
+  <si>
+    <t>Sovato’s system-agnostic platform is designed to remote-enable any surgical, interventional, or diagnostic robotic system, allowing physicians to perform these procedures remotely.</t>
+  </si>
+  <si>
+    <t>Nyxoah</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nyxoah directly competes with Inspire Medical in the sleep respiratory market. Both offer alternatives to the traditional sleep apnea therapies: CPAP and BiPAP machines. </t>
+  </si>
+  <si>
+    <t>Distalmotion</t>
+  </si>
+  <si>
+    <t>Company plans to use the funding to accelerate the U.S. commercial adoption of Dexter, its soft tissue surgical robot system.</t>
+  </si>
+  <si>
+    <t>Revival Healthcare Capital</t>
+  </si>
+  <si>
+    <t>Orchestra Biomed</t>
+  </si>
+  <si>
+    <t>Surgical Automations</t>
+  </si>
+  <si>
+    <t>Endoscopic robot featuring autonomous capabilities</t>
+  </si>
+  <si>
+    <t>Dr. Fred Moll, TurboStart</t>
+  </si>
+  <si>
+    <t>Multi-asset portfolio of therapeutic solutions for cardiovascular disease, hypertensions and other indications</t>
+  </si>
+  <si>
+    <t>Intelerad</t>
+  </si>
+  <si>
+    <t>Medical imaging software provider: cloud-enabled and intelligent solutions in radiology and cardiology</t>
+  </si>
+  <si>
+    <t>Abbott</t>
+  </si>
+  <si>
+    <t>Exact Sciences</t>
+  </si>
+  <si>
+    <t>Exact Sciences develops cancer screening and diagnostic tests. Its portfolio includes the flagship Cologuard, a non-invasive test to screen for colorectal cancer. It provides an alternative to colonoscopy that requires no bowel preparation, sedation and clinical visits. The test can take place at home by collecting a stool sample and mailing it to a lab.</t>
+  </si>
+  <si>
+    <t>Acera</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Acera’s portfolio centers on Restrata, a fully resorbable, electrospun fiber matrix that resembles human extracellular matrix. Applied to hard-to-heal, complex wounds, the synthetic fibers support cell ingrowth, retention and differentiation. </t>
+  </si>
+  <si>
+    <t>Okami</t>
+  </si>
+  <si>
+    <t>The company has developed technology that it claims could make vascular embolization faster and better. It competes with embolization coils such as Boston Scientific’s Interlock and Terumo’s Azur.</t>
+  </si>
+  <si>
+    <t>Gilde Healthcare, Vensana Capital, U.S. Venture Partners</t>
+  </si>
+  <si>
+    <t>Allegheny Performance Plastics</t>
+  </si>
+  <si>
+    <t>Holbrook Tool and Molding, Inc</t>
+  </si>
+  <si>
+    <t>Precision injection molding and tooling company based in Meadville, Pennsylvania. This strategic acquisition strengthens Allegheny's capabilities in precision tooling and complex component manufacturing, while expanding its footprint in the North American market.</t>
+  </si>
+  <si>
+    <t>Alpha RT</t>
+  </si>
+  <si>
+    <t>A pioneer in remote MRI scanning solutions and services. The transaction creates a comprehensive remote-imaging portfolio, combining Alpha RT's staffing services and training programs with DeepHealth’s existing FDA-cleared TechLive™ remote scanning technology.</t>
+  </si>
+  <si>
+    <t>Hims &amp; Hers</t>
+  </si>
+  <si>
+    <t>YourBio Health</t>
+  </si>
+  <si>
+    <t>YourBio Health develops technologies designed to simplify the process and expand when, where, and how blood samples can be collected—including beyond traditional clinic settings. Its TAP® device, built on HALO™ technology, uses bladeless microneedles thinner than an eyelash to produce high-quality capillary blood samples in seconds, without the pain or complexity of traditional methods, like fingerstick or venipuncture. </t>
+  </si>
+  <si>
+    <t>Decemeber</t>
+  </si>
+  <si>
+    <t>NeuWave (J&amp;J)</t>
+  </si>
+  <si>
+    <t>Quantum Surgical</t>
+  </si>
+  <si>
+    <t>NeuWave’s microwave ablation system is used in percutaneous tumor ablation procedures, where needles are inserted through the skin to treat the tumor</t>
+  </si>
+  <si>
+    <t>Q1 2026</t>
+  </si>
+  <si>
+    <t>Oncology</t>
+  </si>
+  <si>
+    <t>Valencia</t>
+  </si>
+  <si>
+    <t>Valencia makes the eCoin tibial nerve stimulator, which received Food and Drug Administration approval in 2022 to treat urinary urge incontinence. The leadless device is implanted near the ankle</t>
+  </si>
+  <si>
+    <t>MetaSight Diagnostics</t>
+  </si>
+  <si>
+    <t>Guardant</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MetaSight uses mass spectrometry multi-omics technology to find biomarkers associated with acute and chronic diseases in serum samples. Tests for colorectal cancer, an area of focus for Guardant, and liver disease-associated fibrosis were MetaSight’s two most advanced programs just before the acquisition.  </t>
+  </si>
+  <si>
+    <t>Integrity Orthopaedics</t>
+  </si>
+  <si>
+    <t>Smith &amp; Nephew</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Integrity received 510(k) clearance for Tendon Seam in 2023. Physicians use the system to reattach soft tissue to bone in orthopedic surgical procedures. </t>
+  </si>
+  <si>
+    <t>CathWorks</t>
+  </si>
+  <si>
+    <t>CathWorks FFRangio System, a non-invasive technology used to evaluate coronary artery disease</t>
+  </si>
+  <si>
+    <t>Masimo</t>
+  </si>
+  <si>
+    <t>Danaher</t>
+  </si>
+  <si>
+    <t>A leading specialty diagnostics provider of pulse oximetry and other patient monitoring solutions, primarily in acute care settings</t>
+  </si>
+  <si>
+    <t>Penumbra</t>
+  </si>
+  <si>
+    <t>Penumbra makes heart devices to remove clots from blood vessels, treating conditions including pulmonary embolism, stroke and deep vein thrombosis. It also makes an embolization system, designed to stop blood flow to control bleeding.</t>
+  </si>
+  <si>
+    <t>Conformal Medical</t>
+  </si>
+  <si>
+    <t>W. L. Gore &amp; Associates</t>
+  </si>
+  <si>
+    <t>Conformal Medical, a clinical-stage company developing the CLAASⓇ AcuForm™ System for left atrial appendage occlusion</t>
+  </si>
+  <si>
+    <t>Vivasure Medical</t>
+  </si>
+  <si>
+    <t>Haemonetics</t>
+  </si>
+  <si>
+    <t>Vivasure is focused on the development of advanced polymer implants and delivery systems, primarily focused on minimally invasive vessel closure in cardiology, interventional radiology, and vascular surgery. In 2022, Vivasure Medical received a strategic investment from Haemonetics, which included an option to acquire Vivasure Medical.</t>
+  </si>
+  <si>
+    <t>Scientia Vascular</t>
+  </si>
+  <si>
+    <t>Scientia’s neurovascular access devices are used to navigate the brain’s complex vasculature to treat conditions such as strokes and aneurysms.</t>
+  </si>
+  <si>
+    <t>Biocare Medical</t>
+  </si>
+  <si>
+    <t>Agilent</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Biocare’s antibody, reagent and instrument business complements Agilent’s offerings in clinical and research pathology and includes immunohistochemistry and in situ hybridization, Agilent said. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Paris-based Gleamer has received Food and Drug Administration clearance for four devices and has CE marks for six products. The portfolio includes BoneView, software that identifies fractures during reviews of X-rays. Other Gleamer products find lung nodules on CT scans and multiple sclerosis lesions on brain MRI scans.
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Undisclosed </t>
+  </si>
+  <si>
+    <t>Radiology</t>
+  </si>
+  <si>
+    <t>Owen Mumford</t>
+  </si>
+  <si>
+    <t>Embecta</t>
+  </si>
+  <si>
+    <t>United Kingdom-based Owen Mumford makes autoinjectors, lancets and other medical products. The company has some overlap with Embecta on pen needles and syringes, but Embecta focuses on insulin administration while Owen Mumford’s offerings are broader</t>
+  </si>
+  <si>
+    <t>Q1 2027</t>
+  </si>
+  <si>
+    <t>Diabetes Care</t>
   </si>
 </sst>
 </file>
@@ -2768,7 +3048,7 @@
     <numFmt numFmtId="164" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
     <numFmt numFmtId="165" formatCode="&quot;$&quot;#,##0"/>
   </numFmts>
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -2780,6 +3060,7 @@
       <b/>
       <sz val="11"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="11"/>
@@ -2794,6 +3075,12 @@
       <color rgb="FFFFFFFF"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="3">
@@ -2838,7 +3125,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="44" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
@@ -2861,12 +3148,45 @@
     <xf numFmtId="6" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Currency" xfId="1" builtinId="4"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="1">
+  <dxfs count="4">
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -3175,7 +3495,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I105"/>
+  <dimension ref="A1:I126"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="40.5703125" customWidth="1"/>
@@ -4029,7 +4349,7 @@
         <v>881</v>
       </c>
     </row>
-    <row r="33" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>113</v>
       </c>
@@ -4055,7 +4375,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="34" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>143</v>
       </c>
@@ -4081,7 +4401,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="35" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>120</v>
       </c>
@@ -4107,7 +4427,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="36" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>85</v>
       </c>
@@ -4133,7 +4453,7 @@
         <v>876</v>
       </c>
     </row>
-    <row r="37" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>311</v>
       </c>
@@ -4159,7 +4479,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="38" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>128</v>
       </c>
@@ -4185,7 +4505,7 @@
         <v>876</v>
       </c>
     </row>
-    <row r="39" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>133</v>
       </c>
@@ -4211,7 +4531,7 @@
         <v>875</v>
       </c>
     </row>
-    <row r="40" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>136</v>
       </c>
@@ -4237,7 +4557,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="41" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>140</v>
       </c>
@@ -4263,7 +4583,7 @@
         <v>876</v>
       </c>
     </row>
-    <row r="42" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>91</v>
       </c>
@@ -4289,7 +4609,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="43" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
         <v>198</v>
       </c>
@@ -4306,7 +4626,7 @@
         <v>533000000</v>
       </c>
       <c r="F43" t="s">
-        <v>200</v>
+        <v>251</v>
       </c>
       <c r="G43" t="s">
         <v>201</v>
@@ -4314,8 +4634,11 @@
       <c r="H43" t="s">
         <v>880</v>
       </c>
-    </row>
-    <row r="44" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I43" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="44" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
         <v>149</v>
       </c>
@@ -4341,7 +4664,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="45" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
         <v>152</v>
       </c>
@@ -4367,7 +4690,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="46" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
         <v>155</v>
       </c>
@@ -4393,7 +4716,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="47" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
         <v>208</v>
       </c>
@@ -4419,7 +4742,7 @@
         <v>876</v>
       </c>
     </row>
-    <row r="48" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
         <v>110</v>
       </c>
@@ -5930,19 +6253,572 @@
         <v>878</v>
       </c>
     </row>
+    <row r="106" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A106" t="s">
+        <v>911</v>
+      </c>
+      <c r="B106" t="s">
+        <v>910</v>
+      </c>
+      <c r="C106" t="s">
+        <v>11</v>
+      </c>
+      <c r="D106" t="s">
+        <v>912</v>
+      </c>
+      <c r="E106" s="6">
+        <v>465000000</v>
+      </c>
+      <c r="F106" t="s">
+        <v>251</v>
+      </c>
+      <c r="G106" t="s">
+        <v>913</v>
+      </c>
+      <c r="H106" t="s">
+        <v>874</v>
+      </c>
+    </row>
+    <row r="107" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A107" t="s">
+        <v>918</v>
+      </c>
+      <c r="B107" t="s">
+        <v>917</v>
+      </c>
+      <c r="C107" t="s">
+        <v>11</v>
+      </c>
+      <c r="D107" t="s">
+        <v>919</v>
+      </c>
+      <c r="E107" s="6">
+        <v>225000000</v>
+      </c>
+      <c r="F107" t="s">
+        <v>251</v>
+      </c>
+      <c r="G107" t="s">
+        <v>913</v>
+      </c>
+      <c r="H107" t="s">
+        <v>878</v>
+      </c>
+    </row>
+    <row r="108" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A108" t="s">
+        <v>945</v>
+      </c>
+      <c r="B108" t="s">
+        <v>279</v>
+      </c>
+      <c r="C108" t="s">
+        <v>11</v>
+      </c>
+      <c r="D108" t="s">
+        <v>946</v>
+      </c>
+      <c r="E108" s="6">
+        <v>2300000000</v>
+      </c>
+      <c r="F108" t="s">
+        <v>251</v>
+      </c>
+      <c r="G108" t="s">
+        <v>913</v>
+      </c>
+      <c r="H108" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="109" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A109" t="s">
+        <v>948</v>
+      </c>
+      <c r="B109" t="s">
+        <v>947</v>
+      </c>
+      <c r="C109" t="s">
+        <v>11</v>
+      </c>
+      <c r="D109" t="s">
+        <v>949</v>
+      </c>
+      <c r="E109" s="6">
+        <v>21000000000</v>
+      </c>
+      <c r="F109" t="s">
+        <v>251</v>
+      </c>
+      <c r="G109" t="s">
+        <v>913</v>
+      </c>
+      <c r="H109" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="110" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A110" t="s">
+        <v>950</v>
+      </c>
+      <c r="B110" t="s">
+        <v>82</v>
+      </c>
+      <c r="C110" t="s">
+        <v>11</v>
+      </c>
+      <c r="D110" t="s">
+        <v>951</v>
+      </c>
+      <c r="E110" s="6">
+        <v>725000000</v>
+      </c>
+      <c r="F110" t="s">
+        <v>251</v>
+      </c>
+      <c r="G110" t="s">
+        <v>913</v>
+      </c>
+      <c r="H110" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="111" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A111" t="s">
+        <v>956</v>
+      </c>
+      <c r="B111" t="s">
+        <v>955</v>
+      </c>
+      <c r="C111" t="s">
+        <v>11</v>
+      </c>
+      <c r="D111" t="s">
+        <v>957</v>
+      </c>
+      <c r="E111" t="s">
+        <v>19</v>
+      </c>
+      <c r="F111" t="s">
+        <v>251</v>
+      </c>
+      <c r="G111" t="s">
+        <v>201</v>
+      </c>
+      <c r="H111" t="s">
+        <v>875</v>
+      </c>
+    </row>
+    <row r="112" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A112" t="s">
+        <v>958</v>
+      </c>
+      <c r="B112" t="s">
+        <v>147</v>
+      </c>
+      <c r="C112" t="s">
+        <v>11</v>
+      </c>
+      <c r="D112" t="s">
+        <v>959</v>
+      </c>
+      <c r="E112" t="s">
+        <v>19</v>
+      </c>
+      <c r="F112" t="s">
+        <v>251</v>
+      </c>
+      <c r="G112" t="s">
+        <v>913</v>
+      </c>
+      <c r="H112" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="113" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A113" t="s">
+        <v>961</v>
+      </c>
+      <c r="B113" t="s">
+        <v>960</v>
+      </c>
+      <c r="C113" t="s">
+        <v>11</v>
+      </c>
+      <c r="D113" t="s">
+        <v>962</v>
+      </c>
+      <c r="E113" t="s">
+        <v>19</v>
+      </c>
+      <c r="F113" t="s">
+        <v>251</v>
+      </c>
+      <c r="G113" t="s">
+        <v>963</v>
+      </c>
+      <c r="H113" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="114" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A114" t="s">
+        <v>964</v>
+      </c>
+      <c r="B114" t="s">
+        <v>965</v>
+      </c>
+      <c r="C114" t="s">
+        <v>11</v>
+      </c>
+      <c r="D114" t="s">
+        <v>966</v>
+      </c>
+      <c r="E114" t="s">
+        <v>19</v>
+      </c>
+      <c r="F114" t="s">
+        <v>967</v>
+      </c>
+      <c r="G114" t="s">
+        <v>66</v>
+      </c>
+      <c r="H114" t="s">
+        <v>968</v>
+      </c>
+    </row>
+    <row r="115" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A115" t="s">
+        <v>969</v>
+      </c>
+      <c r="B115" t="s">
+        <v>92</v>
+      </c>
+      <c r="C115" t="s">
+        <v>11</v>
+      </c>
+      <c r="D115" t="s">
+        <v>970</v>
+      </c>
+      <c r="E115" t="s">
+        <v>19</v>
+      </c>
+      <c r="F115" t="s">
+        <v>967</v>
+      </c>
+      <c r="G115" t="s">
+        <v>14</v>
+      </c>
+      <c r="H115" t="s">
+        <v>880</v>
+      </c>
+    </row>
+    <row r="116" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A116" t="s">
+        <v>971</v>
+      </c>
+      <c r="B116" t="s">
+        <v>972</v>
+      </c>
+      <c r="C116" t="s">
+        <v>11</v>
+      </c>
+      <c r="D116" t="s">
+        <v>973</v>
+      </c>
+      <c r="E116" s="3">
+        <v>59000000</v>
+      </c>
+      <c r="F116" t="s">
+        <v>967</v>
+      </c>
+      <c r="G116" t="s">
+        <v>66</v>
+      </c>
+      <c r="H116" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="117" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A117" t="s">
+        <v>974</v>
+      </c>
+      <c r="B117" t="s">
+        <v>975</v>
+      </c>
+      <c r="C117" t="s">
+        <v>11</v>
+      </c>
+      <c r="D117" t="s">
+        <v>976</v>
+      </c>
+      <c r="E117" s="3">
+        <v>450000000</v>
+      </c>
+      <c r="F117" t="s">
+        <v>967</v>
+      </c>
+      <c r="G117" t="s">
+        <v>14</v>
+      </c>
+      <c r="H117" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="118" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A118" t="s">
+        <v>977</v>
+      </c>
+      <c r="B118" t="s">
+        <v>71</v>
+      </c>
+      <c r="C118" t="s">
+        <v>11</v>
+      </c>
+      <c r="D118" t="s">
+        <v>978</v>
+      </c>
+      <c r="E118" s="3">
+        <v>585000000</v>
+      </c>
+      <c r="F118" t="s">
+        <v>967</v>
+      </c>
+      <c r="G118" t="s">
+        <v>66</v>
+      </c>
+      <c r="H118" t="s">
+        <v>876</v>
+      </c>
+    </row>
+    <row r="119" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A119" t="s">
+        <v>979</v>
+      </c>
+      <c r="B119" t="s">
+        <v>980</v>
+      </c>
+      <c r="C119" t="s">
+        <v>11</v>
+      </c>
+      <c r="D119" t="s">
+        <v>981</v>
+      </c>
+      <c r="E119" s="3">
+        <v>9900000000</v>
+      </c>
+      <c r="F119" t="s">
+        <v>967</v>
+      </c>
+      <c r="G119" t="s">
+        <v>66</v>
+      </c>
+      <c r="H119" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="120" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A120" t="s">
+        <v>982</v>
+      </c>
+      <c r="B120" t="s">
+        <v>92</v>
+      </c>
+      <c r="C120" t="s">
+        <v>11</v>
+      </c>
+      <c r="D120" t="s">
+        <v>983</v>
+      </c>
+      <c r="E120" s="3">
+        <v>14500000000</v>
+      </c>
+      <c r="F120" t="s">
+        <v>967</v>
+      </c>
+      <c r="G120" t="s">
+        <v>14</v>
+      </c>
+      <c r="H120" t="s">
+        <v>876</v>
+      </c>
+    </row>
+    <row r="121" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A121" t="s">
+        <v>984</v>
+      </c>
+      <c r="B121" t="s">
+        <v>985</v>
+      </c>
+      <c r="C121" t="s">
+        <v>11</v>
+      </c>
+      <c r="D121" t="s">
+        <v>986</v>
+      </c>
+      <c r="E121" t="s">
+        <v>19</v>
+      </c>
+      <c r="F121" t="s">
+        <v>967</v>
+      </c>
+      <c r="G121" t="s">
+        <v>66</v>
+      </c>
+      <c r="H121" t="s">
+        <v>876</v>
+      </c>
+    </row>
+    <row r="122" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A122" t="s">
+        <v>987</v>
+      </c>
+      <c r="B122" t="s">
+        <v>988</v>
+      </c>
+      <c r="C122" t="s">
+        <v>11</v>
+      </c>
+      <c r="D122" t="s">
+        <v>989</v>
+      </c>
+      <c r="E122" s="3">
+        <v>215000000</v>
+      </c>
+      <c r="F122" t="s">
+        <v>967</v>
+      </c>
+      <c r="G122" t="s">
+        <v>14</v>
+      </c>
+      <c r="H122" t="s">
+        <v>876</v>
+      </c>
+    </row>
+    <row r="123" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A123" t="s">
+        <v>990</v>
+      </c>
+      <c r="B123" t="s">
+        <v>71</v>
+      </c>
+      <c r="C123" t="s">
+        <v>11</v>
+      </c>
+      <c r="D123" t="s">
+        <v>991</v>
+      </c>
+      <c r="E123" s="3">
+        <v>550000000</v>
+      </c>
+      <c r="F123" t="s">
+        <v>967</v>
+      </c>
+      <c r="G123" t="s">
+        <v>94</v>
+      </c>
+      <c r="H123" t="s">
+        <v>876</v>
+      </c>
+    </row>
+    <row r="124" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A124" t="s">
+        <v>992</v>
+      </c>
+      <c r="B124" t="s">
+        <v>993</v>
+      </c>
+      <c r="C124" t="s">
+        <v>11</v>
+      </c>
+      <c r="D124" t="s">
+        <v>994</v>
+      </c>
+      <c r="E124" s="3">
+        <v>950000000</v>
+      </c>
+      <c r="F124" t="s">
+        <v>967</v>
+      </c>
+      <c r="G124" t="s">
+        <v>94</v>
+      </c>
+      <c r="H124" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="125" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A125" t="s">
+        <v>247</v>
+      </c>
+      <c r="B125" t="s">
+        <v>147</v>
+      </c>
+      <c r="C125" t="s">
+        <v>11</v>
+      </c>
+      <c r="D125" s="10" t="s">
+        <v>995</v>
+      </c>
+      <c r="E125" t="s">
+        <v>996</v>
+      </c>
+      <c r="F125" t="s">
+        <v>967</v>
+      </c>
+      <c r="G125" t="s">
+        <v>94</v>
+      </c>
+      <c r="H125" t="s">
+        <v>997</v>
+      </c>
+    </row>
+    <row r="126" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A126" t="s">
+        <v>998</v>
+      </c>
+      <c r="B126" t="s">
+        <v>999</v>
+      </c>
+      <c r="C126" t="s">
+        <v>11</v>
+      </c>
+      <c r="D126" t="s">
+        <v>1000</v>
+      </c>
+      <c r="E126" s="3">
+        <v>201000000</v>
+      </c>
+      <c r="F126" t="s">
+        <v>1001</v>
+      </c>
+      <c r="G126" t="s">
+        <v>124</v>
+      </c>
+      <c r="H126" t="s">
+        <v>1002</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:I105" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <autoFilter ref="A1:I111" xr:uid="{00000000-0001-0000-0000-000000000000}">
     <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:I104">
       <sortCondition descending="1" ref="E1:E104"/>
     </sortState>
   </autoFilter>
+  <phoneticPr fontId="4" type="noConversion"/>
+  <conditionalFormatting sqref="A114:A1048576 A1:A107 A110 B109:B111 B113">
+    <cfRule type="duplicateValues" dxfId="3" priority="4"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B108">
+    <cfRule type="duplicateValues" dxfId="2" priority="1"/>
+  </conditionalFormatting>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:I190"/>
+  <dimension ref="A1:I201"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="27" customWidth="1"/>
@@ -10942,14 +11818,295 @@
         <v>214</v>
       </c>
     </row>
+    <row r="191" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A191" t="s">
+        <v>914</v>
+      </c>
+      <c r="B191" t="s">
+        <v>333</v>
+      </c>
+      <c r="C191" t="s">
+        <v>915</v>
+      </c>
+      <c r="D191" s="8">
+        <v>200000000</v>
+      </c>
+      <c r="E191" t="s">
+        <v>916</v>
+      </c>
+      <c r="F191" t="s">
+        <v>251</v>
+      </c>
+      <c r="G191" t="s">
+        <v>913</v>
+      </c>
+      <c r="H191" t="s">
+        <v>880</v>
+      </c>
+    </row>
+    <row r="192" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A192" t="s">
+        <v>920</v>
+      </c>
+      <c r="B192" t="s">
+        <v>333</v>
+      </c>
+      <c r="C192" t="s">
+        <v>921</v>
+      </c>
+      <c r="D192" s="8">
+        <v>75000000</v>
+      </c>
+      <c r="E192" t="s">
+        <v>922</v>
+      </c>
+      <c r="F192" t="s">
+        <v>251</v>
+      </c>
+      <c r="G192" t="s">
+        <v>913</v>
+      </c>
+      <c r="H192" t="s">
+        <v>876</v>
+      </c>
+    </row>
+    <row r="193" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A193" t="s">
+        <v>923</v>
+      </c>
+      <c r="B193" t="s">
+        <v>333</v>
+      </c>
+      <c r="C193" t="s">
+        <v>924</v>
+      </c>
+      <c r="D193" s="8">
+        <v>200000000</v>
+      </c>
+      <c r="E193" t="s">
+        <v>925</v>
+      </c>
+      <c r="F193" t="s">
+        <v>251</v>
+      </c>
+      <c r="G193" t="s">
+        <v>913</v>
+      </c>
+      <c r="H193" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="194" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A194" t="s">
+        <v>926</v>
+      </c>
+      <c r="B194" t="s">
+        <v>333</v>
+      </c>
+      <c r="C194" t="s">
+        <v>928</v>
+      </c>
+      <c r="E194" t="s">
+        <v>927</v>
+      </c>
+      <c r="F194" t="s">
+        <v>251</v>
+      </c>
+      <c r="G194" t="s">
+        <v>913</v>
+      </c>
+      <c r="H194" t="s">
+        <v>880</v>
+      </c>
+    </row>
+    <row r="195" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A195" t="s">
+        <v>929</v>
+      </c>
+      <c r="B195" t="s">
+        <v>333</v>
+      </c>
+      <c r="C195" t="s">
+        <v>930</v>
+      </c>
+      <c r="D195" s="8">
+        <v>43000000</v>
+      </c>
+      <c r="E195" t="s">
+        <v>931</v>
+      </c>
+      <c r="F195" t="s">
+        <v>251</v>
+      </c>
+      <c r="G195" t="s">
+        <v>913</v>
+      </c>
+      <c r="H195" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="196" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A196" t="s">
+        <v>932</v>
+      </c>
+      <c r="B196" t="s">
+        <v>333</v>
+      </c>
+      <c r="C196" t="s">
+        <v>934</v>
+      </c>
+      <c r="D196" s="8">
+        <v>41000000</v>
+      </c>
+      <c r="E196" t="s">
+        <v>933</v>
+      </c>
+      <c r="F196" t="s">
+        <v>251</v>
+      </c>
+      <c r="G196" t="s">
+        <v>913</v>
+      </c>
+      <c r="H196" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="197" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A197" t="s">
+        <v>935</v>
+      </c>
+      <c r="B197" t="s">
+        <v>339</v>
+      </c>
+      <c r="C197" t="s">
+        <v>936</v>
+      </c>
+      <c r="D197" s="8">
+        <v>77000000</v>
+      </c>
+      <c r="F197" t="s">
+        <v>251</v>
+      </c>
+      <c r="G197" t="s">
+        <v>913</v>
+      </c>
+      <c r="H197" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="198" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A198" t="s">
+        <v>937</v>
+      </c>
+      <c r="B198" t="s">
+        <v>333</v>
+      </c>
+      <c r="C198" t="s">
+        <v>938</v>
+      </c>
+      <c r="D198" s="8">
+        <v>150000000</v>
+      </c>
+      <c r="E198" t="s">
+        <v>939</v>
+      </c>
+      <c r="F198" t="s">
+        <v>251</v>
+      </c>
+      <c r="G198" t="s">
+        <v>913</v>
+      </c>
+      <c r="H198" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="199" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A199" t="s">
+        <v>940</v>
+      </c>
+      <c r="B199" t="s">
+        <v>333</v>
+      </c>
+      <c r="C199" t="s">
+        <v>944</v>
+      </c>
+      <c r="D199" s="8">
+        <v>30000000</v>
+      </c>
+      <c r="E199" t="s">
+        <v>212</v>
+      </c>
+      <c r="F199" t="s">
+        <v>251</v>
+      </c>
+      <c r="G199" t="s">
+        <v>913</v>
+      </c>
+      <c r="H199" t="s">
+        <v>876</v>
+      </c>
+    </row>
+    <row r="200" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A200" t="s">
+        <v>941</v>
+      </c>
+      <c r="B200" t="s">
+        <v>333</v>
+      </c>
+      <c r="C200" t="s">
+        <v>942</v>
+      </c>
+      <c r="D200" s="8">
+        <v>3400000</v>
+      </c>
+      <c r="E200" t="s">
+        <v>943</v>
+      </c>
+      <c r="F200" t="s">
+        <v>251</v>
+      </c>
+      <c r="G200" t="s">
+        <v>913</v>
+      </c>
+      <c r="H200" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="201" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A201" t="s">
+        <v>952</v>
+      </c>
+      <c r="B201" t="s">
+        <v>333</v>
+      </c>
+      <c r="C201" t="s">
+        <v>953</v>
+      </c>
+      <c r="D201" s="8">
+        <v>45000000</v>
+      </c>
+      <c r="E201" t="s">
+        <v>954</v>
+      </c>
+      <c r="F201" t="s">
+        <v>251</v>
+      </c>
+      <c r="G201" t="s">
+        <v>913</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:I181" xr:uid="{00000000-0001-0000-0100-000000000000}">
     <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:I181">
       <sortCondition descending="1" ref="D1:D181"/>
     </sortState>
   </autoFilter>
+  <phoneticPr fontId="4" type="noConversion"/>
+  <conditionalFormatting sqref="A1:A1048576">
+    <cfRule type="duplicateValues" dxfId="1" priority="1"/>
+  </conditionalFormatting>
   <conditionalFormatting sqref="C7">
-    <cfRule type="duplicateValues" dxfId="0" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="3"/>
   </conditionalFormatting>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" r:id="rId1"/>

--- a/MedTech_Deals.xlsx
+++ b/MedTech_Deals.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://beacononehcp-my.sharepoint.com/personal/hannah_peric_beacononehcp_com/Documents/Documents/medtech-dashboard/medtech-dashboard/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="533" documentId="13_ncr:1_{A8E36CAE-087B-4CF0-B739-AC648A6297F4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{575DBBF2-A508-4237-B004-99B605644AA8}"/>
+  <xr:revisionPtr revIDLastSave="534" documentId="13_ncr:1_{A8E36CAE-087B-4CF0-B739-AC648A6297F4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A03232DD-7FED-42C2-9009-824559C6FEE8}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2950,10 +2950,10 @@
     <t>Embecta</t>
   </si>
   <si>
-    <t>United Kingdom-based Owen Mumford makes autoinjectors, lancets and other medical products. The company has some overlap with Embecta on pen needles and syringes, but Embecta focuses on insulin administration while Owen Mumford’s offerings are broader</t>
-  </si>
-  <si>
     <t>Diabetes Care</t>
+  </si>
+  <si>
+    <t>United Kingdom-based Owen Mumford makes autoinjectors, lancets and other medical products. The company has some overlap with Embecta on pen needles and syringes, but Embecta focuses on insulin administration while Owen Mumford’s offerings are broader.</t>
   </si>
 </sst>
 </file>
@@ -4541,7 +4541,7 @@
         <v>123</v>
       </c>
       <c r="H44" t="s">
-        <v>975</v>
+        <v>974</v>
       </c>
     </row>
     <row r="45" spans="1:8" x14ac:dyDescent="0.25">
@@ -6661,7 +6661,7 @@
         <v>10</v>
       </c>
       <c r="D126" t="s">
-        <v>974</v>
+        <v>975</v>
       </c>
       <c r="E126" s="2">
         <v>201000000</v>
@@ -6673,7 +6673,7 @@
         <v>123</v>
       </c>
       <c r="H126" t="s">
-        <v>975</v>
+        <v>974</v>
       </c>
     </row>
   </sheetData>
